--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -684,25 +684,25 @@
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 298676억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 298674억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 296027억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 296804억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 294666억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 295424억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 292177억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 292916억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1821,25 +1821,25 @@
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 298676억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 298674억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 296027억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 296804억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 294666억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 295424억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 292177억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 292916억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -6646,16 +6646,16 @@
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.225627</v>
+        <v>0.225607</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.131941</v>
+        <v>0.134914</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.06147</v>
+        <v>0.064191</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.011542</v>
+        <v>0.014093</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6798,16 +6798,16 @@
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.052027</v>
+        <v>0.052028</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.052018</v>
+        <v>0.052024</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.052023</v>
+        <v>0.05203</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.052021</v>
+        <v>0.052025</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6953,16 +6953,16 @@
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013339</v>
+        <v>0.01334</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013339</v>
+        <v>0.013335</v>
       </c>
       <c r="AM23" s="24" t="n">
+        <v>0.013341</v>
+      </c>
+      <c r="AN23" s="24" t="n">
         <v>0.013328</v>
-      </c>
-      <c r="AN23" s="24" t="n">
-        <v>0.013332</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7540,13 +7540,13 @@
         <v>0.219858</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.219715</v>
+        <v>0.220118</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.220162</v>
+        <v>0.219653</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.220605</v>
+        <v>0.220112</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7920,13 +7920,13 @@
         <v>0.058052</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>0.035609</v>
+        <v>0.036711</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>0.017908</v>
+        <v>0.018625</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>0.003494</v>
+        <v>0.004193</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8540,13 +8540,13 @@
         <v>0.038122</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.03661</v>
+        <v>0.036666</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.036123</v>
+        <v>0.036228</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036107</v>
+        <v>0.036204</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8668,13 +8668,13 @@
         <v>0.032973</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.031727</v>
+        <v>0.031775</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.0315</v>
+        <v>0.031592</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.031627</v>
+        <v>0.031714</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9312,13 +9312,13 @@
         <v>-0.343146</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.171651</v>
+        <v>-0.172847</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.138714</v>
+        <v>-0.141236</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.092728</v>
+        <v>-0.09472999999999999</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9735,16 +9735,16 @@
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.013339</v>
+        <v>0.01334</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.013339</v>
+        <v>0.013335</v>
       </c>
       <c r="AM45" s="24" t="n">
+        <v>0.013341</v>
+      </c>
+      <c r="AN45" s="24" t="n">
         <v>0.013328</v>
-      </c>
-      <c r="AN45" s="24" t="n">
-        <v>0.013332</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -678,31 +678,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 288846억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289784억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 298674억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 303133억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 296804억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 308660억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 295424억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 319501억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 292916억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 333694억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -942,7 +942,7 @@
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 220억 × 0.09% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 221억 × 0.09% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1815,31 +1815,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 288846억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289784억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 298674억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 303133억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 296804억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 308660억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 295424억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 319501억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 292916억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 333694억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2294,7 +2294,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 220억 × 0.09% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 221억 × 0.09% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4450,7 +4450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.2, "op_wape_pct": 622.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 393.21, "rev_act": 485.14, "op_pred": -59.92, "op_act": 0.32}, {"q": "2025Q4", "rev_pred": 427.6, "rev_act": 533.85, "op_pred": -65.16, "op_act": 21.67}, {"q": "2026Q1", "rev_pred": 424.35, "rev_act": 506.2, "op_pred": -64.67, "op_act": 13.94}, {"q": "2026Q2", "rev_pred": 424.35, "rev_act": 491.36, "op_pred": -64.67, "op_act": 12.78}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.2, "op_wape_pct": 622.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 24.8, "wape_trend": 39.8, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 393.21, "rev_act": 485.14, "op_pred": -59.92, "op_act": 0.32}, {"q": "2025Q4", "rev_pred": 427.6, "rev_act": 533.85, "op_pred": -65.16, "op_act": 21.67}, {"q": "2026Q1", "rev_pred": 424.35, "rev_act": 506.2, "op_pred": -64.67, "op_act": 13.94}, {"q": "2026Q2", "rev_pred": 424.35, "rev_act": 491.36, "op_pred": -64.67, "op_act": 12.78}]}</t>
         </is>
       </c>
     </row>
@@ -6642,20 +6642,20 @@
         <v>0.233064</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.241338</v>
+        <v>0.245372</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.225607</v>
+        <v>0.243918</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.134914</v>
+        <v>0.180246</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.064191</v>
+        <v>0.150923</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.014093</v>
+        <v>0.151524</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6791,23 +6791,23 @@
         <v>0.052022</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.052029</v>
+        <v>0.052027</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.052028</v>
+        <v>0.052027</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.052024</v>
+        <v>0.052026</v>
       </c>
       <c r="AM22" s="24" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.05203</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.052025</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6946,23 +6946,23 @@
         <v>0.013339</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013334</v>
+        <v>0.013336</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.01334</v>
+        <v>0.013331</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013335</v>
+        <v>0.013342</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013341</v>
+        <v>0.013338</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013328</v>
+        <v>0.013329</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7530,23 +7530,23 @@
         <v>0.220172</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.219955</v>
+        <v>0.220339</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.219858</v>
+        <v>0.220023</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.220118</v>
+        <v>0.219818</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.219653</v>
+        <v>0.220085</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.220112</v>
+        <v>0.219823</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7913,20 +7913,20 @@
         <v>0.057576</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>0.063545</v>
+        <v>0.06466</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>0.058052</v>
+        <v>0.062921</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>0.036711</v>
+        <v>0.048825</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>0.018625</v>
+        <v>0.043696</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>0.004193</v>
+        <v>0.046422</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8169,7 +8169,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
@@ -8533,20 +8533,20 @@
         <v>0.039647</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.041383</v>
+        <v>0.041564</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.038122</v>
+        <v>0.038635</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.036666</v>
+        <v>0.038087</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.036228</v>
+        <v>0.0391</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036204</v>
+        <v>0.040979</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8661,20 +8661,20 @@
         <v>0.033858</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.035539</v>
+        <v>0.035694</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.032973</v>
+        <v>0.033416</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.031775</v>
+        <v>0.03306</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.031592</v>
+        <v>0.034057</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.031714</v>
+        <v>0.035963</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9305,20 +9305,20 @@
       <c r="AG42" s="31" t="n"/>
       <c r="AH42" s="31" t="n"/>
       <c r="AI42" s="24" t="n">
-        <v>-0.444609</v>
+        <v>-0.44535</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.343146</v>
+        <v>-0.346366</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.172847</v>
+        <v>-0.184211</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.141236</v>
+        <v>-0.169609</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.09472999999999999</v>
+        <v>-0.152305</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9437,7 +9437,7 @@
         <v>-0.057971</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.044118</v>
+        <v>-0.058824</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -9728,23 +9728,23 @@
         <v>0.013339</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.013334</v>
+        <v>0.013336</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.01334</v>
+        <v>0.013331</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.013335</v>
+        <v>0.013342</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.013341</v>
+        <v>0.013338</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.013328</v>
+        <v>0.013329</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 288306억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 288281억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 300688억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 300635억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 305237억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 305156억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 315624억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 315516억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 329777억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 329667억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 288306억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 288281억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 300688억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 300635억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 305237억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 305156억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 315624억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 315516억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 329777억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 329667억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4224,7 +4224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5928,35 +5928,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6063,7 +6063,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1006</v>
+        <v>978</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6245,7 +6245,7 @@
         <v>875</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6336,7 +6336,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>998.5</v>
+        <v>991.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6504,20 +6504,20 @@
         <v>0.230705107</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.239018965</v>
+        <v>0.238905855</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.233878954</v>
+        <v>0.233665366</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.167165147</v>
+        <v>0.166858852</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.139135319</v>
+        <v>0.138755348</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.143841765</v>
+        <v>0.143565788</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6818,23 +6818,23 @@
         <v>0.013332012</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013328262</v>
+        <v>0.013329479</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013328927</v>
+        <v>0.013331235</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.01333745</v>
+        <v>0.013340951</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013342422</v>
+        <v>0.013332366</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013341492</v>
+        <v>0.013332624</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7859,36 +7859,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003825829</v>
+        <v>0.003882174</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002457413</v>
+        <v>-0.002390923</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.001217144</v>
+        <v>-0.001139464</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.000185574</v>
+        <v>-9.5753e-05</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.004924938</v>
+        <v>0.005028132</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.001792942</v>
+        <v>-0.001674919</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005340741</v>
+        <v>-0.005206376</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.003381807</v>
+        <v>0.003533641</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.005288412</v>
+        <v>0.006761789</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.001395503</v>
+        <v>-0.006212243</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7987,36 +7987,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.004325829</v>
+        <v>0.004382174</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.002457413</v>
+        <v>-0.002390923</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.001217144</v>
+        <v>-0.001139464</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.000185574</v>
+        <v>-9.5753e-05</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.004924938</v>
+        <v>0.005028132</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.011792942</v>
+        <v>-0.001674919</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.004659259</v>
+        <v>-0.005206376</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.003381807</v>
+        <v>0.003533641</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.005288412</v>
+        <v>0.006761789</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.001395503</v>
+        <v>-0.006212243</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8266,13 +8266,13 @@
         <v>-0.07990430599999999</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.09486185900000001</v>
+        <v>-0.094845084</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.114996849</v>
+        <v>-0.115013251</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.142985781</v>
+        <v>-0.14296484</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8394,13 +8394,13 @@
         <v>0.131439307</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.126896149</v>
+        <v>0.12687371</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.123558812</v>
+        <v>0.123581186</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.121012335</v>
+        <v>0.120994612</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1006</v>
+        <v>978</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.052022626972417</v>
+        <v>0.0520230643317184</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.4602318424916231</v>
+        <v>0.460233589830872</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35752,7 +35752,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37892,7 +37892,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="32">
@@ -37902,7 +37902,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="33">
@@ -37942,7 +37942,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.65</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 288281억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 288260억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 300635억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 300579억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 305156억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 305067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 315516억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 315394억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 329667억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 329534억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 288281억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 288260억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 300635억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 300579억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 305156억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 305067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 315516억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 315394억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 329667억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 329534억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4224,7 +4224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5095,35 +5095,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5928,35 +5928,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6063,7 +6063,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6336,7 +6336,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>991.7</v>
+        <v>988.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6504,20 +6504,20 @@
         <v>0.230705107</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.238905855</v>
+        <v>0.238830449</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.233665366</v>
+        <v>0.233432361</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.166858852</v>
+        <v>0.166516522</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.138755348</v>
+        <v>0.138309296</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.143565788</v>
+        <v>0.143178878</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6818,23 +6818,23 @@
         <v>0.013332012</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013329479</v>
+        <v>0.01333029</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013331235</v>
+        <v>0.013333753</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013340951</v>
+        <v>0.01332942</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013332366</v>
+        <v>0.013337591</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013332624</v>
+        <v>0.013337948</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7859,36 +7859,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003882174</v>
+        <v>0.003826485</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002390923</v>
+        <v>-0.002453518</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.001139464</v>
+        <v>-0.001206129</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-9.5753e-05</v>
+        <v>-0.00017031</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.005028132</v>
+        <v>0.004944484</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.001674919</v>
+        <v>-0.001768547</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005206376</v>
+        <v>-0.005305929</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.003533641</v>
+        <v>0.005625306</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.006761789</v>
+        <v>-0.003357072</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.006212243</v>
+        <v>0.002757642</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7987,36 +7987,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.004382174</v>
+        <v>0.004326485</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.002390923</v>
+        <v>-0.002453518</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.001139464</v>
+        <v>-0.001206129</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-9.5753e-05</v>
+        <v>-0.00017031</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.005028132</v>
+        <v>0.004944484</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.001674919</v>
+        <v>-0.001768547</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.005206376</v>
+        <v>-0.005305929</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.003533641</v>
+        <v>0.005625306</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.006761789</v>
+        <v>-0.003357072</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.006212243</v>
+        <v>0.002757642</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8269,10 +8269,10 @@
         <v>-0.094845084</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.115013251</v>
+        <v>-0.114994718</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.14296484</v>
+        <v>-0.142940905</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8397,10 +8397,10 @@
         <v>0.12687371</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.123581186</v>
+        <v>0.123561273</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.120994612</v>
+        <v>0.120979033</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9063,11 +9063,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 983원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 990원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2199978860585562</v>
+        <v>0.2200025367833587</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0520230643317184</v>
+        <v>0.05202435777831526</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.460233589830872</v>
+        <v>0.4602355530818988</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35752,7 +35752,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37892,7 +37892,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="32">
@@ -37902,7 +37902,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="33">
@@ -37942,7 +37942,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.56</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 277072억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 276806억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 288260억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287522억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 300579억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299804억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 305067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 304886억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 315394억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 316877억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 329534억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 333823억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 277072억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 276806억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 288260억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287522억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 300579억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299804억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 305067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 304886억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 315394억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 316877억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 329534억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 333823억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4224,7 +4224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6501,23 +6501,23 @@
         <v>0.129553029</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.230705107</v>
+        <v>0.229525862</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.238830449</v>
+        <v>0.235644535</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.233432361</v>
+        <v>0.230247956</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.166516522</v>
+        <v>0.165831862</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.138309296</v>
+        <v>0.144758818</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.143178878</v>
+        <v>0.161047203</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6815,26 +6815,26 @@
         <v>0.013332853</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.013332012</v>
+        <v>0.013328262</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.01333029</v>
+        <v>0.013334147</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013333753</v>
+        <v>0.0133367</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.01332942</v>
+        <v>0.013337248</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013337591</v>
+        <v>0.013332948</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013337948</v>
+        <v>0.013337363</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7859,36 +7859,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003826485</v>
+        <v>0.00318258</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002453518</v>
+        <v>-0.00321308</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.001206129</v>
+        <v>-0.002092932</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.00017031</v>
+        <v>-0.001195476</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.004944484</v>
+        <v>-0.004033349</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.001768547</v>
+        <v>0.001285693</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005305929</v>
+        <v>0.004871083</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.005625306</v>
+        <v>-0.00059323</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.003357072</v>
+        <v>-0.008595524</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.002757642</v>
+        <v>0.010170508</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7987,36 +7987,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.004326485</v>
+        <v>0.00368258</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.002453518</v>
+        <v>-0.00321308</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.001206129</v>
+        <v>-0.002092932</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.00017031</v>
+        <v>-0.001195476</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.004944484</v>
+        <v>-0.004033349</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.001768547</v>
+        <v>0.001285693</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.005305929</v>
+        <v>0.004871083</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.005625306</v>
+        <v>-0.00059323</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.003357072</v>
+        <v>-0.008595524</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.002757642</v>
+        <v>0.010170508</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8259,20 +8259,20 @@
         <v>-0.058586296</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.068600673</v>
+        <v>-0.068557546</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.07990430599999999</v>
+        <v>-0.079869739</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.094845084</v>
+        <v>-0.09483713000000001</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.114994718</v>
+        <v>-0.115039656</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.142940905</v>
+        <v>-0.143144317</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8387,20 +8387,20 @@
         <v>0.142937331</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.13785931</v>
+        <v>0.137772642</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.131439307</v>
+        <v>0.131398537</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.12687371</v>
+        <v>0.126887946</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.123561273</v>
+        <v>0.123633322</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.120979033</v>
+        <v>0.121160561</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200025367833587</v>
+        <v>0.2200029590176062</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202435777831526</v>
+        <v>0.05202202922552682</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.4602355530818988</v>
+        <v>0.4602159195779293</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287522억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287510억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299804억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299791억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 304886억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 304873억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 316877억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 316863억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 333823억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 333821억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287522억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287510억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299804억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299791억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 304886억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 304873억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 316877억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 316863억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 333823억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 333821억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5095,35 +5095,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5214,35 +5214,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5333,35 +5333,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5452,35 +5452,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5571,35 +5571,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5690,35 +5690,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5809,35 +5809,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5928,35 +5928,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6063,7 +6063,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>966</v>
+        <v>999</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6245,7 +6245,7 @@
         <v>875</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6336,7 +6336,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>988.2</v>
+        <v>995</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6504,20 +6504,20 @@
         <v>0.229525862</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.235644535</v>
+        <v>0.235606832</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.230247956</v>
+        <v>0.230209122</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.165831862</v>
+        <v>0.16577781</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.144758818</v>
+        <v>0.144709209</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.161047203</v>
+        <v>0.161067375</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6818,23 +6818,23 @@
         <v>0.013328262</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013334147</v>
+        <v>0.013334554</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.0133367</v>
+        <v>0.013337121</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013337248</v>
+        <v>0.013337867</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013332948</v>
+        <v>0.013333526</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013337363</v>
+        <v>0.013337538</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7875,20 +7875,20 @@
         <v>-0.004033349</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.001285693</v>
+        <v>0.001285757</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
         <v>0.004871083</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.00059323</v>
+        <v>-0.0005929210000000001</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.008595524</v>
+        <v>0.001404573</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.010170508</v>
+        <v>0.000170362</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8003,20 +8003,20 @@
         <v>-0.004033349</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.001285693</v>
+        <v>0.001285757</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
         <v>0.004871083</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.00059323</v>
+        <v>-0.0005929210000000001</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.008595524</v>
+        <v>0.001404573</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.010170508</v>
+        <v>0.000170362</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -9063,11 +9063,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>966</v>
+        <v>999</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 990원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 980원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202202922552682</v>
+        <v>0.05202296943159693</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35752,7 +35752,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37892,7 +37892,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.65</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="32">
@@ -37902,7 +37902,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
@@ -37942,7 +37942,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.51</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -681,37 +681,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 276806억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 277599억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287510억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289467억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299791억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 302149억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 304873억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 316863억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 317683억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 333821억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332605억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 276806억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 277599억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287510억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289467억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299791억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 302149억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 304873억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 316863억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 317683억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 333821억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332605억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2004,121 +2004,121 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 165억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 165억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 195억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 180억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 228억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 196억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 264억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 211억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 303억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 227억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 346억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 243억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 394억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 259억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 446억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 276억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 502억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 293억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 564억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 310억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 165억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 165억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 195억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 180억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 228억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 196억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 264억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 211억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 303억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 227억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 346억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 243억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 394억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 259억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 446억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 276억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 502억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 293억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 564억 × 46.02%(주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 310억 × 0.09%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 1014억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3483,12 +3483,6 @@
       <text>
         <t>추정: 직전 결산 DPS 0원 유지
 [abs]</t>
-      </text>
-    </comment>
-    <comment ref="AC35" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[valuation]</t>
       </text>
     </comment>
     <comment ref="AD35" authorId="0" shapeId="0">
@@ -4224,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4346,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -1.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 22.02% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -1.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4367,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 46.02% / 부채 0.00% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.4602, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2022Q1~2023Q2)", "debt": null}</t>
+          <t>· 이자율 자산 0.09% / 부채 0.00% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0009, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 46.0% 클립 — 주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la))", "debt": null}</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4419,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 연결 손익 없는 분기 7개는 별도 재무제표로 보충(셀 src 표기; fin issues no_cons_statements·no_prior_ytd; 겹치는 마지막 분기 2026Q2 연결/별도 매출 +1.8%): 2021Q4, 2022Q1, 2022Q2, 2022Q3, 2022Q4, 2023Q1, 2023Q2 / 금융손익 실적→추정 단절: 최근 4분기 실적 -30/-15/-14/-14(중위 -14억) → 추정 2026Q3 +19억(차 +33억, +233%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 연결 손익 없는 분기 7개는 별도 재무제표로 보충(셀 src 표기; fin issues no_cons_statements·no_prior_ytd; 겹치는 마지막 분기 2026Q2 연결/별도 매출 +1.8%): 2021Q4, 2022Q1, 2022Q2, 2022Q3, 2022Q4, 2023Q1, 2023Q2 / 이자발생자산 이자율: 주석 연율 46.0% 이상(주석 연율 46.0% &gt; 상한 20% · 주석/CF 508.90배 · CF 창 2025Q3~2026Q2(= la)) → CF 연율 0.1% 로 클립(assumptions.interest_rate_check) / 금융손익 실적→추정 단절: 최근 4분기 실적 -30/-15/-14/-14(중위 -14억) → 추정 2026Q3 +0억(차 +14억, +100%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -6501,23 +6495,23 @@
         <v>0.129553029</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.229525862</v>
+        <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.235606832</v>
+        <v>0.244014629</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.230209122</v>
+        <v>0.239878837</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.16577781</v>
+        <v>0.174155886</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.144709209</v>
+        <v>0.144395343</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.161067375</v>
+        <v>0.149022579</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6815,26 +6809,26 @@
         <v>0.013332853</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.013328262</v>
+        <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013334554</v>
+        <v>0.013335354</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013337121</v>
+        <v>0.01334273</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013337867</v>
+        <v>0.013334766</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013333526</v>
+        <v>0.013342363</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013337538</v>
+        <v>0.013333509</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7859,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.00318258</v>
+        <v>0.000410193</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.00321308</v>
+        <v>-0.005496361</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002092932</v>
+        <v>0.001310428</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.001195476</v>
+        <v>-0.002656071</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004033349</v>
+        <v>-0.00178087</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.001285757</v>
+        <v>-0.005210338</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.004871083</v>
+        <v>0.009457511</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.0005929210000000001</v>
+        <v>-0.00500445</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.001404573</v>
+        <v>0.00248034</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.000170362</v>
+        <v>-0.001613654</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7987,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.00368258</v>
+        <v>0.000910193</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.00321308</v>
+        <v>-0.005496361</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002092932</v>
+        <v>0.001310428</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.001195476</v>
+        <v>-0.002656071</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004033349</v>
+        <v>-0.00178087</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.001285757</v>
+        <v>-0.005210338</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.004871083</v>
+        <v>-0.0005424889999999999</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.0005929210000000001</v>
+        <v>0.00499555</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.001404573</v>
+        <v>0.00248034</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.000170362</v>
+        <v>-0.001613654</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8243,36 +8237,36 @@
         <v/>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>-0.033974239</v>
+        <v>-0.017075663</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>-0.038789081</v>
+        <v>-0.017830609</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>-0.043782794</v>
+        <v>-0.017977023</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.050439498</v>
+        <v>-0.018799572</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.058586296</v>
+        <v>-0.019834407</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.068557546</v>
+        <v>-0.020924063</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.079869739</v>
+        <v>-0.021102817</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.09483713000000001</v>
+        <v>-0.021727492</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.115039656</v>
+        <v>-0.022797347</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.143144317</v>
+        <v>-0.024257987</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8371,36 +8365,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.180059807</v>
+        <v>0.090500077</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.168289433</v>
+        <v>0.08517717499999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.156285639</v>
+        <v>0.077724973</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.1488942</v>
+        <v>0.074063537</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.142937331</v>
+        <v>0.071384425</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.137772642</v>
+        <v>0.068894474</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.131398537</v>
+        <v>0.06360587500000001</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.126887946</v>
+        <v>0.060345765</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.123633322</v>
+        <v>0.058381187</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.121160561</v>
+        <v>0.057356931</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9338,7 +9332,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200029590176062</v>
+        <v>0.2202002931118711</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9377,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202296943159693</v>
+        <v>0.05202427723116311</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9455,11 +9449,11 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.4602159195779293</v>
+        <v>0.0009239466175731165</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.4602)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0009)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -9494,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0</v>
+        <v>5.875565788663742e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9929,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12013,7 +12007,12 @@
       <c r="N32" s="18" t="n">
         <v>13311.6</v>
       </c>
-      <c r="P32" s="9" t="n"/>
+      <c r="O32" s="18" t="n">
+        <v>307.76</v>
+      </c>
+      <c r="P32" s="37" t="n">
+        <v>307.76</v>
+      </c>
       <c r="Q32" s="18" t="n">
         <v>367.28</v>
       </c>
@@ -13381,10 +13380,10 @@
       <c r="F52" s="9" t="n"/>
       <c r="K52" s="9" t="n"/>
       <c r="O52" s="18" t="n">
-        <v>402.67</v>
+        <v>710.4299999999999</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>402.67</v>
+        <v>710.4299999999999</v>
       </c>
       <c r="Q52" s="18" t="n">
         <v>759.71</v>
@@ -13514,7 +13513,12 @@
       </c>
       <c r="F54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
-      <c r="P54" s="9" t="n"/>
+      <c r="O54" s="18" t="n">
+        <v>307.76</v>
+      </c>
+      <c r="P54" s="37" t="n">
+        <v>307.76</v>
+      </c>
       <c r="Q54" s="18" t="n">
         <v>367.28</v>
       </c>
@@ -16211,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29357,10 +29361,7 @@
         <v/>
       </c>
       <c r="AB35" s="15" t="n"/>
-      <c r="AC35" s="39">
-        <f>IFERROR(변수!$D$42/(Y32+AA32+AB32+AC32),"")</f>
-        <v/>
-      </c>
+      <c r="AC35" s="39" t="n"/>
       <c r="AD35" s="39">
         <f>IFERROR(변수!$D$42/(AA32+AB32+AC32+AD32),"")</f>
         <v/>
@@ -37872,7 +37873,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>264.7</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="30">
@@ -37892,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.77</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="32">
@@ -37912,7 +37913,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1949</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="34">
@@ -37922,7 +37923,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.17</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="35">
@@ -37932,7 +37933,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 289467억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289464억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 302149억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 302178억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307128억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 317683억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 317776억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 332605억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332730억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 289467억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289464억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 302149억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 302178억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307067억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307128억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 317683억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 317776억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 332605억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332730억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5089,35 +5089,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5922,35 +5922,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6057,7 +6057,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6330,7 +6330,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>995</v>
+        <v>992.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6498,20 +6498,20 @@
         <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.244014629</v>
+        <v>0.243995777</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.239878837</v>
+        <v>0.23999534</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.174155886</v>
+        <v>0.174390112</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.144395343</v>
+        <v>0.144725126</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.149022579</v>
+        <v>0.149479459</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013335354</v>
+        <v>0.013335556</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.01334273</v>
+        <v>0.013341476</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013334766</v>
+        <v>0.013332106</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013342363</v>
+        <v>0.013338519</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013333509</v>
+        <v>0.013341595</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7853,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000410193</v>
+        <v>0.000587956</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005496361</v>
+        <v>-0.005304948</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001310428</v>
+        <v>0.001496398</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.002656071</v>
+        <v>-0.002455916</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.00178087</v>
+        <v>-0.001562227</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.005210338</v>
+        <v>-0.004972718</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.009457511</v>
+        <v>-0.000312619</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.00500445</v>
+        <v>0.005231689</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00248034</v>
+        <v>-0.007269951</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001613654</v>
+        <v>0.006459169</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7981,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.000910193</v>
+        <v>0.001087956</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.005496361</v>
+        <v>-0.005304948</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.001310428</v>
+        <v>0.001496398</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.002656071</v>
+        <v>-0.002455916</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.00178087</v>
+        <v>-0.001562227</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.005210338</v>
+        <v>-0.004972718</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.0005424889999999999</v>
+        <v>-0.000312619</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.00499555</v>
+        <v>0.005231689</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.00248034</v>
+        <v>-0.007269951</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.001613654</v>
+        <v>0.006459169</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8263,10 +8263,10 @@
         <v>-0.021727492</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.022797347</v>
+        <v>-0.022810694</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.024257987</v>
+        <v>-0.024258318</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8385,16 +8385,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.06360587500000001</v>
+        <v>0.063644424</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060345765</v>
+        <v>0.060307335</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.058381187</v>
+        <v>0.058415368</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.057356931</v>
+        <v>0.057355078</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 980원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 966원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2202002931118711</v>
+        <v>0.2201734033459519</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202427723116311</v>
+        <v>0.05202348136469864</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0009239466175731165</v>
+        <v>0.0009238928550423802</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>5.875565788663742e-06</v>
+        <v>5.864885036406156e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.9</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="32">
@@ -37903,7 +37903,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33">
@@ -37943,7 +37943,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.63</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 289464억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289459억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 302178억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 302160억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307128억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307097억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 317776억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 317732억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 332730억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332678억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 289464억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289459억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 302178억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 302160억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307128억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307097억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 317776억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 317732억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 332730억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332678억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5922,35 +5922,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6498,20 +6498,20 @@
         <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.243995777</v>
+        <v>0.243976926</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.23999534</v>
+        <v>0.239917672</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.174390112</v>
+        <v>0.174282008</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.144725126</v>
+        <v>0.144576724</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.149479459</v>
+        <v>0.149315027</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013335556</v>
+        <v>0.013335758</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013341476</v>
+        <v>0.013342312</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013332106</v>
+        <v>0.013333333</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013338519</v>
+        <v>0.013340248</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013341595</v>
+        <v>0.01333052</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7853,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000587956</v>
+        <v>0.000410455</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005304948</v>
+        <v>-0.005496193</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001496398</v>
+        <v>0.0013105</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.002455916</v>
+        <v>-0.002656095</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.001562227</v>
+        <v>-0.001780992</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004972718</v>
+        <v>-0.005210649</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.000312619</v>
+        <v>0.009457135</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.005231689</v>
+        <v>-0.005005287</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.007269951</v>
+        <v>0.00247946</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.006459169</v>
+        <v>-0.011612641</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7981,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.001087956</v>
+        <v>0.000910455</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.005304948</v>
+        <v>-0.005496193</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.001496398</v>
+        <v>0.0013105</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.002455916</v>
+        <v>-0.002656095</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.001562227</v>
+        <v>-0.001780992</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.004972718</v>
+        <v>-0.005210649</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.000312619</v>
+        <v>-0.000542865</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.005231689</v>
+        <v>0.004994713</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.007269951</v>
+        <v>0.00247946</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.006459169</v>
+        <v>-0.011612641</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8385,10 +8385,10 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.063644424</v>
+        <v>0.06360587500000001</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060307335</v>
+        <v>0.060345765</v>
       </c>
       <c r="AM34" s="24" t="n">
         <v>0.058415368</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2201734033459519</v>
+        <v>0.2202002931118711</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202348136469864</v>
+        <v>0.0520245708460487</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0009238928550423802</v>
+        <v>0.0009239144789189104</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>5.864885036406156e-06</v>
+        <v>5.869002849802198e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6330,7 +6330,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>992.4</v>
+        <v>989.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.68</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="32">
@@ -37903,7 +37903,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="33">
@@ -37943,7 +37943,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.58</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 289459억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289449억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 302160억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 302092억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307097억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 306971억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 317732억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 317544억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 332678억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332441억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 289459억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289449억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 302160억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 302092억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307097억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 306971억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 317732억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 317544억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 332678억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332441억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5922,35 +5922,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6057,7 +6057,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6330,7 +6330,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>989.3</v>
+        <v>990.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6498,20 +6498,20 @@
         <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.243976926</v>
+        <v>0.243939223</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.239917672</v>
+        <v>0.239645832</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.174282008</v>
+        <v>0.173795539</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.144576724</v>
+        <v>0.143900669</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.149315027</v>
+        <v>0.148516352</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013335758</v>
+        <v>0.013336162</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013342312</v>
+        <v>0.013329574</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013333333</v>
+        <v>0.013338859</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013340248</v>
+        <v>0.013333718</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.01333052</v>
+        <v>0.013340195</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7853,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000410455</v>
+        <v>0.000410135</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005496193</v>
+        <v>-0.005496367</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.0013105</v>
+        <v>0.001310473</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.002656095</v>
+        <v>-0.002655976</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.001780992</v>
+        <v>-0.001780722</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.005210649</v>
+        <v>-0.005210326</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.009457135</v>
+        <v>0.001659531</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.005005287</v>
+        <v>-0.005004481</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00247946</v>
+        <v>-0.005319091</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.011612641</v>
+        <v>0.008387026000000001</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7981,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.000910455</v>
+        <v>0.000910135</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.005496193</v>
+        <v>-0.005496367</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.0013105</v>
+        <v>0.001310473</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.002656095</v>
+        <v>-0.002655976</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.001780992</v>
+        <v>-0.001780722</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.005210649</v>
+        <v>-0.005210326</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.000542865</v>
+        <v>0.001659531</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.004994713</v>
+        <v>-0.005004481</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.00247946</v>
+        <v>-0.005319091</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.011612641</v>
+        <v>0.008387026000000001</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8257,16 +8257,16 @@
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.021102817</v>
+        <v>-0.021090035</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.021727492</v>
+        <v>-0.021727209</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.022810694</v>
+        <v>-0.022810389</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.024258318</v>
+        <v>-0.024244328</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8388,13 +8388,13 @@
         <v>0.06360587500000001</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060345765</v>
+        <v>0.060309521</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.058415368</v>
+        <v>0.058417365</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.057355078</v>
+        <v>0.057324635</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 966원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,000원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0520245708460487</v>
+        <v>0.05202331090219096</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0009239144789189104</v>
+        <v>0.0009239638922769186</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>5.869002849802198e-06</v>
+        <v>5.878672128573719e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.48</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="32">
@@ -37943,7 +37943,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.54</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 289449억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289447억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 302092억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 302147억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 306971억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307082억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 317544억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 317709억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 332441억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332661억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 289449억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289447억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 302092억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 302147억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 306971억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307082억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 317544억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 317709억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 332441억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332661억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5922,35 +5922,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6057,7 +6057,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6330,7 +6330,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>990.6</v>
+        <v>988.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6498,20 +6498,20 @@
         <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.243939223</v>
+        <v>0.243920371</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.239645832</v>
+        <v>0.23985942</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.173795539</v>
+        <v>0.174209938</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.143900669</v>
+        <v>0.144494278</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.148516352</v>
+        <v>0.149306661</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013336162</v>
+        <v>0.013336364</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013329574</v>
+        <v>0.013342939</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013338859</v>
+        <v>0.013334152</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013333718</v>
+        <v>0.013341209</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013340195</v>
+        <v>0.013331224</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7853,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000410135</v>
+        <v>0.000410193</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005496367</v>
+        <v>-0.005496361</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001310473</v>
+        <v>0.001310428</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.002655976</v>
+        <v>-0.002656071</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.001780722</v>
+        <v>-0.00178087</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.005210326</v>
+        <v>-0.005210588</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.001659531</v>
+        <v>0.009457533000000001</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.005004481</v>
+        <v>-0.005004534</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.005319091</v>
+        <v>0.00248</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.008387026000000001</v>
+        <v>-0.011613277</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7981,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.000910135</v>
+        <v>0.000910193</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.005496367</v>
+        <v>-0.005496361</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.001310473</v>
+        <v>0.001310428</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.002655976</v>
+        <v>-0.002656071</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.001780722</v>
+        <v>-0.00178087</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.005210326</v>
+        <v>-0.005210588</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.001659531</v>
+        <v>0.009457533000000001</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.005004481</v>
+        <v>-0.005004534</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.005319091</v>
+        <v>0.00248</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.008387026000000001</v>
+        <v>-0.011613277</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8260,13 +8260,13 @@
         <v>-0.021090035</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.021727209</v>
+        <v>-0.021740266</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.022810389</v>
+        <v>-0.022810694</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.024244328</v>
+        <v>-0.024244659</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8388,13 +8388,13 @@
         <v>0.06360587500000001</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060309521</v>
+        <v>0.060345765</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.058417365</v>
+        <v>0.058381187</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.057324635</v>
+        <v>0.057356931</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 973원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202331090219096</v>
+        <v>0.05202291296188549</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0009239638922769186</v>
+        <v>0.000923946617573112</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>5.878672128573719e-06</v>
+        <v>5.875565788662651e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.55</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="32">
@@ -37943,7 +37943,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 289447억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 289784억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 302147억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 302690억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307082억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307619억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 317709억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 318076억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 332661억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332398억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 289447억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 289784억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 302147억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 302690억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307082억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307619억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 317709억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 318076억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 332661억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332398억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.02% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -1.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -1.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5922,35 +5922,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6057,7 +6057,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>977</v>
+        <v>1017</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6239,7 +6239,7 @@
         <v>875</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6330,7 +6330,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>988.8</v>
+        <v>999</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6498,20 +6498,20 @@
         <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.243920371</v>
+        <v>0.245371941</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.23985942</v>
+        <v>0.242092387</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.174209938</v>
+        <v>0.176263918</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.144494278</v>
+        <v>0.145813409</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.149306661</v>
+        <v>0.147058824</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013336364</v>
+        <v>0.013335957</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013342939</v>
+        <v>0.013334584</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013334152</v>
+        <v>0.013341503</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013341209</v>
+        <v>0.013340241</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013331224</v>
+        <v>0.013341779</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7853,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000410193</v>
+        <v>0.001475221</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005496361</v>
+        <v>-0.004349216</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001310428</v>
+        <v>0.002425205</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.002656071</v>
+        <v>-0.001455955</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.00178087</v>
+        <v>-0.000469621</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.005210588</v>
+        <v>0.004014725</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.009457533000000001</v>
+        <v>-0.001360904</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.005004534</v>
+        <v>0.002005923</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00248</v>
+        <v>0.001784648</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.011613277</v>
+        <v>2.9868e-05</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7981,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.000910193</v>
+        <v>0.001975221</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.005496361</v>
+        <v>-0.004349216</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.001310428</v>
+        <v>0.002425205</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.002656071</v>
+        <v>-0.001455955</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.00178087</v>
+        <v>-0.000469621</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.005210588</v>
+        <v>0.004014725</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.009457533000000001</v>
+        <v>-0.001360904</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.005004534</v>
+        <v>0.002005923</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.00248</v>
+        <v>0.001784648</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.011613277</v>
+        <v>2.9868e-05</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8253,20 +8253,20 @@
         <v>-0.019834407</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.020924063</v>
+        <v>-0.020936577</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.021090035</v>
+        <v>-0.021103087</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.021740266</v>
+        <v>-0.021753891</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.022810694</v>
+        <v>-0.022824955</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.024244659</v>
+        <v>-0.024245984</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8381,20 +8381,20 @@
         <v>0.071384425</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.068894474</v>
+        <v>0.068935679</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.06360587500000001</v>
+        <v>0.06364197100000001</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060345765</v>
+        <v>0.060377632</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.058381187</v>
+        <v>0.058409378</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.057356931</v>
+        <v>0.057349522</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>977</v>
+        <v>1017</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 973원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,024원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2202002931118711</v>
+        <v>0.2200390529655846</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202291296188549</v>
+        <v>0.05202297935494651</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.000923946617573112</v>
+        <v>0.0009237157548006883</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>5.875565788662651e-06</v>
+        <v>5.830985369618026e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.53</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="32">
@@ -37903,7 +37903,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
@@ -37943,7 +37943,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.55</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/133820_model.xlsx
+++ b/argus/kship/models/133820_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 289784억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 290035억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 302690억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 303144억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307619억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 308113억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 318076억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 318486억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 332398억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 332377억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 289784억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 290035억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 302690억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 303144억 × 비례계수 0.0087 × 계절비중 Q1 0.243(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307619억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 308113억 × 비례계수 0.0087 × 계절비중 Q2 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 318076억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 318486억 × 비례계수 0.0087 × 계절비중 Q3 0.251(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 332398억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 332377억 × 비례계수 0.0087 × 계절비중 Q4 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4218,7 +4218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -1.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 22.01% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 -1.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5922,35 +5922,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6057,7 +6057,7 @@
         <v>1004</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1017</v>
+        <v>899</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6239,7 +6239,7 @@
         <v>875</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>927</v>
+        <v>870</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6330,7 +6330,7 @@
         <v>1003.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>999</v>
+        <v>980.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6498,20 +6498,20 @@
         <v>0.233043266</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.245371941</v>
+        <v>0.24644648</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.242092387</v>
+        <v>0.243956428</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.176263918</v>
+        <v>0.178155742</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.145813409</v>
+        <v>0.147280942</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.147058824</v>
+        <v>0.145994344</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.013339709</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.013335957</v>
+        <v>0.013339585</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.013334584</v>
+        <v>0.013330212</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.013341503</v>
+        <v>0.013335372</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.013340241</v>
+        <v>0.013337549</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.013341779</v>
+        <v>0.013329462</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7853,36 +7853,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.001475221</v>
+        <v>0.001203147</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.004349216</v>
+        <v>-0.004643232</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.002425205</v>
+        <v>0.002138665</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.001455955</v>
+        <v>-0.001765279</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.000469621</v>
+        <v>-0.000808385</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.004014725</v>
+        <v>0.001444668</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.001360904</v>
+        <v>-0.003920253</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.002005923</v>
+        <v>-0.000558754</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.001784648</v>
+        <v>-0.000802137</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>2.9868e-05</v>
+        <v>0.001810989</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7981,36 +7981,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.001975221</v>
+        <v>0.001703147</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.004349216</v>
+        <v>-0.004643232</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.002425205</v>
+        <v>0.002138665</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.001455955</v>
+        <v>-0.001765279</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.000469621</v>
+        <v>-0.000808385</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.004014725</v>
+        <v>0.001444668</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.001360904</v>
+        <v>-0.003920253</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.002005923</v>
+        <v>-0.000558754</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.001784648</v>
+        <v>-0.000802137</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>2.9868e-05</v>
+        <v>-0.008189011</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8257,16 +8257,16 @@
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.021103087</v>
+        <v>-0.021128651</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.021753891</v>
+        <v>-0.021767517</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.022824955</v>
+        <v>-0.022825869</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.024245984</v>
+        <v>-0.024246978</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8385,16 +8385,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.06364197100000001</v>
+        <v>0.063719066</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060377632</v>
+        <v>0.060409494</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.058409378</v>
+        <v>0.058437564</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.057349522</v>
+        <v>0.057309828</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1017</v>
+        <v>899</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,024원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 914원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200390529655846</v>
+        <v>0.2200805172624131</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05202297935494651</v>
+        <v>0.05202495731029481</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0009237157548006883</v>
+        <v>0.0009234922131647168</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>5.830985369618026e-06</v>
+        <v>5.787192687259227e-06</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.21</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="32">
@@ -37903,7 +37903,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="33">
@@ -37943,7 +37943,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.69</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="37">
